--- a/precios_competencia.xlsx.xlsx
+++ b/precios_competencia.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mystic\Métricas\DashboardPrecios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94066EF2-FEE0-43CE-BE51-40A9F6A09DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03796682-E281-4DD7-816D-1A56231EB84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1117,7 +1117,7 @@
         <v>280.48</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1399817</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
         <v>1399814</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>1399565</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="4">
         <v>1399564</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>1399563</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="4">
         <v>1399562</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>202.69</v>
       </c>
     </row>
-    <row r="152" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="4">
         <v>1399424</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>327.47000000000003</v>
       </c>
     </row>
-    <row r="157" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
         <v>1399419</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="172" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="4">
         <v>1396820</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="173" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="2">
         <v>1396819</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>699.82</v>
       </c>
     </row>
-    <row r="197" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A197" s="2">
         <v>1396785</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>318.20999999999998</v>
       </c>
     </row>
-    <row r="198" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A198" s="4">
         <v>1396784</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="217" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A217" s="2">
         <v>1396405</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="220" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A220" s="4">
         <v>1396400</v>
       </c>
@@ -12021,7 +12021,7 @@
         <v>186.76</v>
       </c>
     </row>
-    <row r="238" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A238" s="4">
         <v>1396375</v>
       </c>
@@ -15264,7 +15264,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="307" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A307" s="2">
         <v>1392580</v>
       </c>
@@ -15311,7 +15311,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="308" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A308" s="4">
         <v>1392579</v>
       </c>
@@ -15358,7 +15358,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="309" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A309" s="2">
         <v>1392578</v>
       </c>
@@ -15405,7 +15405,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="310" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A310" s="4">
         <v>1392577</v>
       </c>
@@ -18178,7 +18178,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="369" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A369" s="2">
         <v>1392072</v>
       </c>
@@ -18225,7 +18225,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="370" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A370" s="4">
         <v>1392071</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="373" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A373" s="2">
         <v>1392068</v>
       </c>
@@ -18413,7 +18413,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="374" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A374" s="4">
         <v>1392067</v>
       </c>
@@ -19306,7 +19306,7 @@
         <v>699.82</v>
       </c>
     </row>
-    <row r="393" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A393" s="2">
         <v>1392038</v>
       </c>
@@ -19447,7 +19447,7 @@
         <v>202.69</v>
       </c>
     </row>
-    <row r="396" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A396" s="4">
         <v>1392035</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>269.93</v>
       </c>
     </row>
-    <row r="397" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A397" s="2">
         <v>1392034</v>
       </c>
@@ -19543,21 +19543,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O397" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="semana 3"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <filters>
-        <filter val="Karen Jimar Chang Peña"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="11">
-      <filters>
-        <filter val="Mystic"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="12">
       <filters>
         <filter val="CONGELADOR 1 PUERTA 150L"/>
